--- a/artfynd/A 40018-2026 artfynd.xlsx
+++ b/artfynd/A 40018-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,6 +1093,2204 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122230946</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137094256</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>524439</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6616378</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137094256</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137094302</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>524601</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6616383</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-05-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137094302</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137094337</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>524473</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6616259</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137094337</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137094350</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>524727</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6616338</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-05-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137094350</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137094354</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>524559</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6616311</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2016-05-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2016-05-15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137094354</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137094528</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>524616</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6616321</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2014-05-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2014-05-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137094528</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137094620</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>524575</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6616219</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2014-05-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2014-05-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137094620</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137094628</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>524560</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6616261</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-05-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137094628</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137094635</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>524453</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6616355</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2013-05-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2013-05-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137094635</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137095090</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>524366</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6616312</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2011-05-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2011-05-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095090</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137095114</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>524472</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6616099</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2010-05-16</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2010-05-16</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095114</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137095120</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>524473</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6616149</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095120</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137095138</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>524411</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6616245</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2009-05-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2009-05-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095138</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137095152</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>524497</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6616313</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2008-05-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2008-05-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095152</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137095162</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>524692</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6616420</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2007-05-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2007-05-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095162</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137095169</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>524572</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6616439</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2005-05-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2005-05-19</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095169</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137095193</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>524387</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6616381</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2000-05-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2000-05-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095193</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137095214</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>524492</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6616237</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>1999-04-29</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1999-04-29</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095214</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137095238</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Spårudden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>524352</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6616261</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>1995-05-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>1995-05-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Linn Svensson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gunnar Jansson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137095238</t>
         </is>
       </c>
     </row>
@@ -1102,6 +3300,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40018-2026 artfynd.xlsx
+++ b/artfynd/A 40018-2026 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>137094256</v>
       </c>
       <c r="B6" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137094302</v>
       </c>
       <c r="B7" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137094337</v>
       </c>
       <c r="B8" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137094350</v>
       </c>
       <c r="B9" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>137094354</v>
       </c>
       <c r="B10" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137094528</v>
       </c>
       <c r="B11" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137094620</v>
       </c>
       <c r="B12" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137094628</v>
       </c>
       <c r="B13" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137094635</v>
       </c>
       <c r="B14" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137095090</v>
       </c>
       <c r="B15" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137095114</v>
       </c>
       <c r="B16" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137095120</v>
       </c>
       <c r="B17" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>137095138</v>
       </c>
       <c r="B18" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>137095152</v>
       </c>
       <c r="B19" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137095162</v>
       </c>
       <c r="B20" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>137095169</v>
       </c>
       <c r="B21" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>137095193</v>
       </c>
       <c r="B22" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137095214</v>
       </c>
       <c r="B23" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>137095238</v>
       </c>
       <c r="B24" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 40018-2026 artfynd.xlsx
+++ b/artfynd/A 40018-2026 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>137094256</v>
       </c>
       <c r="B6" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137094302</v>
       </c>
       <c r="B7" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>137094337</v>
       </c>
       <c r="B8" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137094350</v>
       </c>
       <c r="B9" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>137094354</v>
       </c>
       <c r="B10" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>137094528</v>
       </c>
       <c r="B11" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>137094620</v>
       </c>
       <c r="B12" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>137094628</v>
       </c>
       <c r="B13" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137094635</v>
       </c>
       <c r="B14" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>137095090</v>
       </c>
       <c r="B15" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>137095114</v>
       </c>
       <c r="B16" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>137095120</v>
       </c>
       <c r="B17" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>137095138</v>
       </c>
       <c r="B18" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>137095152</v>
       </c>
       <c r="B19" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>137095162</v>
       </c>
       <c r="B20" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>137095169</v>
       </c>
       <c r="B21" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
         <v>137095193</v>
       </c>
       <c r="B22" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137095214</v>
       </c>
       <c r="B23" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>137095238</v>
       </c>
       <c r="B24" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 40018-2026 artfynd.xlsx
+++ b/artfynd/A 40018-2026 artfynd.xlsx
@@ -1131,21 +1131,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1253,16 +1241,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1371,17 +1351,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1489,17 +1461,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1607,17 +1571,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1726,11 +1682,7 @@
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
@@ -1839,16 +1791,8 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -2064,11 +2008,7 @@
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2178,16 +2118,8 @@
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2296,11 +2228,7 @@
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2410,11 +2338,7 @@
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2524,11 +2448,7 @@
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2639,11 +2559,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2752,11 +2668,7 @@
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2867,11 +2779,7 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2980,16 +2888,8 @@
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3098,11 +2998,7 @@
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
@@ -3212,16 +3108,8 @@
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>

--- a/artfynd/A 40018-2026 artfynd.xlsx
+++ b/artfynd/A 40018-2026 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>137094256</v>
       </c>
       <c r="B6" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>137094302</v>
       </c>
       <c r="B7" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>137094337</v>
       </c>
       <c r="B8" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>137094350</v>
       </c>
       <c r="B9" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>137094354</v>
       </c>
       <c r="B10" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137094528</v>
       </c>
       <c r="B11" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>137094620</v>
       </c>
       <c r="B12" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>137094628</v>
       </c>
       <c r="B13" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137094635</v>
       </c>
       <c r="B14" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>137095090</v>
       </c>
       <c r="B15" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>137095114</v>
       </c>
       <c r="B16" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137095120</v>
       </c>
       <c r="B17" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137095138</v>
       </c>
       <c r="B18" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137095152</v>
       </c>
       <c r="B19" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>137095162</v>
       </c>
       <c r="B20" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137095169</v>
       </c>
       <c r="B21" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>137095193</v>
       </c>
       <c r="B22" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>137095214</v>
       </c>
       <c r="B23" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>137095238</v>
       </c>
       <c r="B24" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 40018-2026 artfynd.xlsx
+++ b/artfynd/A 40018-2026 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>137094256</v>
       </c>
       <c r="B6" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>137094302</v>
       </c>
       <c r="B7" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>137094337</v>
       </c>
       <c r="B8" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>137094350</v>
       </c>
       <c r="B9" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>137094354</v>
       </c>
       <c r="B10" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137094528</v>
       </c>
       <c r="B11" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>137094620</v>
       </c>
       <c r="B12" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>137094628</v>
       </c>
       <c r="B13" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137094635</v>
       </c>
       <c r="B14" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>137095090</v>
       </c>
       <c r="B15" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>137095114</v>
       </c>
       <c r="B16" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137095120</v>
       </c>
       <c r="B17" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137095138</v>
       </c>
       <c r="B18" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137095152</v>
       </c>
       <c r="B19" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>137095162</v>
       </c>
       <c r="B20" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137095169</v>
       </c>
       <c r="B21" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>137095193</v>
       </c>
       <c r="B22" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>137095214</v>
       </c>
       <c r="B23" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>137095238</v>
       </c>
       <c r="B24" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 40018-2026 artfynd.xlsx
+++ b/artfynd/A 40018-2026 artfynd.xlsx
@@ -1101,7 +1101,7 @@
         <v>137094256</v>
       </c>
       <c r="B6" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>137094302</v>
       </c>
       <c r="B7" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>137094337</v>
       </c>
       <c r="B8" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>137094350</v>
       </c>
       <c r="B9" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>137094354</v>
       </c>
       <c r="B10" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>137094528</v>
       </c>
       <c r="B11" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>137094620</v>
       </c>
       <c r="B12" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>137094628</v>
       </c>
       <c r="B13" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137094635</v>
       </c>
       <c r="B14" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>137095090</v>
       </c>
       <c r="B15" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>137095114</v>
       </c>
       <c r="B16" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>137095120</v>
       </c>
       <c r="B17" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137095138</v>
       </c>
       <c r="B18" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137095152</v>
       </c>
       <c r="B19" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>137095162</v>
       </c>
       <c r="B20" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>137095169</v>
       </c>
       <c r="B21" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2857,7 +2857,7 @@
         <v>137095193</v>
       </c>
       <c r="B22" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>137095214</v>
       </c>
       <c r="B23" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>137095238</v>
       </c>
       <c r="B24" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
